--- a/tests/fixtures/expected/export_validasi.xlsx
+++ b/tests/fixtures/expected/export_validasi.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ringkasan Validasi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ringkasan Masalah" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Preview Sheet Export" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Aturan Rentang Nilai" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Semua Masalah" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Peserta Perlu Dicek" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="NIM di file nilai tidak ada di" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Abjad kosong" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total Nilai kosong" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Nama berbeda antara file pesert" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="NIM duplikat di file nilai" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Nilai tidak valid atau di luar" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Validasi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Masalah" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview Sheet Export" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aturan Rentang Nilai" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semua Masalah" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peserta Perlu Dicek" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIM di file nilai tidak ada di" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abjad kosong" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Nilai kosong" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nama berbeda antara file pesert" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIM duplikat di file nilai" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nilai tidak valid atau di luar" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1711,19 +1711,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kelas Umum</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kode Kelas PAI</t>
@@ -1731,55 +1731,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Nama dari File Nilai</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nama dari File Nilai</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Bacaan</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Bacaan</t>
+          <t>Hafalan</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Hafalan</t>
+          <t>Evaluasi</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Evaluasi</t>
+          <t>Total Nilai</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Total Nilai</t>
+          <t>Abjad</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Abjad</t>
+          <t>Status Nilai</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Status Nilai</t>
+          <t>Status Validasi</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status Validasi</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Catatan Validasi</t>
         </is>
@@ -1793,19 +1788,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240002</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>1A</t>
@@ -1813,31 +1808,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Bagas Pratama</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Belum Ada Nilai</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Belum Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>Abjad kosong; Total Nilai kosong</t>
         </is>
@@ -1851,19 +1841,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240003</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>2B</t>
@@ -1871,27 +1861,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>Siti Rahma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Siti Rahma</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1901,25 +1891,20 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Sudah Ada Nilai</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Sudah Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>Nama berbeda; PRESENSI di luar rentang 0-100</t>
         </is>
@@ -1933,19 +1918,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>240005</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>10A</t>
@@ -1953,12 +1938,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>Eka Wulandari</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eka Wulandari</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1976,28 +1961,23 @@
           <t>90</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Sudah Ada Nilai</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sudah Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>Total Nilai kosong</t>
         </is>
@@ -2011,47 +1991,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>240006</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>10A</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Belum Ada Nilai</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Belum Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>Abjad kosong; Total Nilai kosong</t>
         </is>
@@ -2104,7 +2079,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2202,7 +2177,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2250,7 +2225,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -2294,7 +2269,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -2352,7 +2327,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2404,7 +2379,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -2444,7 +2419,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -2488,7 +2463,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
